--- a/tests/fixtures/drive_eval/files/invoice_2026_03.xlsx
+++ b/tests/fixtures/drive_eval/files/invoice_2026_03.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sample Workshop SL</t>
+          <t>Sample Workshop Lda.</t>
         </is>
       </c>
     </row>
